--- a/artfynd/A 8202-2025 artfynd.xlsx
+++ b/artfynd/A 8202-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131428733</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131428356</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131429717</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>131428762</v>
       </c>
       <c r="B5" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131429166</v>
       </c>
       <c r="B6" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>131428270</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>131429277</v>
       </c>
       <c r="B8" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 8202-2025 artfynd.xlsx
+++ b/artfynd/A 8202-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131428733</v>
       </c>
       <c r="B2" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131428356</v>
       </c>
       <c r="B3" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131429717</v>
       </c>
       <c r="B4" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>131428762</v>
       </c>
       <c r="B5" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131429166</v>
       </c>
       <c r="B6" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>131428270</v>
       </c>
       <c r="B7" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>131429277</v>
       </c>
       <c r="B8" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 8202-2025 artfynd.xlsx
+++ b/artfynd/A 8202-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131428733</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131428356</v>
       </c>
       <c r="B3" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131429717</v>
       </c>
       <c r="B4" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>131428762</v>
       </c>
       <c r="B5" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131429166</v>
       </c>
       <c r="B6" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>131428270</v>
       </c>
       <c r="B7" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>131429277</v>
       </c>
       <c r="B8" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 8202-2025 artfynd.xlsx
+++ b/artfynd/A 8202-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131428733</v>
       </c>
       <c r="B2" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131428356</v>
       </c>
       <c r="B3" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131429717</v>
       </c>
       <c r="B4" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>131428762</v>
       </c>
       <c r="B5" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131429166</v>
       </c>
       <c r="B6" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>131428270</v>
       </c>
       <c r="B7" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>131429277</v>
       </c>
       <c r="B8" t="n">
-        <v>57889</v>
+        <v>57895</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 8202-2025 artfynd.xlsx
+++ b/artfynd/A 8202-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131428733</v>
       </c>
       <c r="B2" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131428356</v>
       </c>
       <c r="B3" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131429717</v>
       </c>
       <c r="B4" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>131428762</v>
       </c>
       <c r="B5" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131429166</v>
       </c>
       <c r="B6" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>131428270</v>
       </c>
       <c r="B7" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>131429277</v>
       </c>
       <c r="B8" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 8202-2025 artfynd.xlsx
+++ b/artfynd/A 8202-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131428733</v>
       </c>
       <c r="B2" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131428356</v>
       </c>
       <c r="B3" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131429717</v>
       </c>
       <c r="B4" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>131428762</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131429166</v>
       </c>
       <c r="B6" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>131428270</v>
       </c>
       <c r="B7" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>131429277</v>
       </c>
       <c r="B8" t="n">
-        <v>57896</v>
+        <v>57899</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 8202-2025 artfynd.xlsx
+++ b/artfynd/A 8202-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131428733</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131428356</v>
       </c>
       <c r="B3" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131429717</v>
       </c>
       <c r="B4" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>131428762</v>
       </c>
       <c r="B5" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131429166</v>
       </c>
       <c r="B6" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>131428270</v>
       </c>
       <c r="B7" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>131429277</v>
       </c>
       <c r="B8" t="n">
-        <v>57899</v>
+        <v>57901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 8202-2025 artfynd.xlsx
+++ b/artfynd/A 8202-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131428733</v>
       </c>
       <c r="B2" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131428356</v>
       </c>
       <c r="B3" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131429717</v>
       </c>
       <c r="B4" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>131428762</v>
       </c>
       <c r="B5" t="n">
-        <v>57904</v>
+        <v>57907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131429166</v>
       </c>
       <c r="B6" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>131428270</v>
       </c>
       <c r="B7" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>131429277</v>
       </c>
       <c r="B8" t="n">
-        <v>57901</v>
+        <v>57904</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 8202-2025 artfynd.xlsx
+++ b/artfynd/A 8202-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131428733</v>
       </c>
       <c r="B2" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>131428356</v>
       </c>
       <c r="B3" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131429717</v>
       </c>
       <c r="B4" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>131428762</v>
       </c>
       <c r="B5" t="n">
-        <v>57907</v>
+        <v>57912</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>131429166</v>
       </c>
       <c r="B6" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>131428270</v>
       </c>
       <c r="B7" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>131429277</v>
       </c>
       <c r="B8" t="n">
-        <v>57904</v>
+        <v>57909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 8202-2025 artfynd.xlsx
+++ b/artfynd/A 8202-2025 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131428733</v>
+        <v>131428270</v>
       </c>
       <c r="B2" t="n">
-        <v>57909</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -704,19 +704,24 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Asprönningen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>490118</v>
+        <v>489929</v>
       </c>
       <c r="R2" t="n">
-        <v>6664831</v>
+        <v>6664736</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:31</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Torrtall med djupa spår efter födosök samt troligt bohål</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,11 +790,11 @@
         <v>131428356</v>
       </c>
       <c r="B3" t="n">
-        <v>57909</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -899,27 +899,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131429717</v>
+        <v>131428733</v>
       </c>
       <c r="B4" t="n">
-        <v>57912</v>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -928,24 +928,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Asprönningen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>489814</v>
+        <v>490118</v>
       </c>
       <c r="R4" t="n">
-        <v>6664870</v>
+        <v>6664831</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Torrtall med djupa spår efter födosök samt troligt bohål</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,27 +1011,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131428762</v>
+        <v>131429166</v>
       </c>
       <c r="B5" t="n">
-        <v>57912</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1040,19 +1040,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Asprönningen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>490118</v>
+        <v>490030</v>
       </c>
       <c r="R5" t="n">
-        <v>6664831</v>
+        <v>6664753</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,12 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:34</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Äldre tall med många ringhack några meter upp på stammen</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,14 +1123,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131429166</v>
+        <v>131429277</v>
       </c>
       <c r="B6" t="n">
-        <v>57909</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1154,7 +1154,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>490030</v>
+        <v>489954</v>
       </c>
       <c r="R6" t="n">
-        <v>6664753</v>
+        <v>6664687</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131428270</v>
+        <v>131428762</v>
       </c>
       <c r="B7" t="n">
-        <v>57909</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,16 +1246,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1264,24 +1264,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Asprönningen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>489929</v>
+        <v>490118</v>
       </c>
       <c r="R7" t="n">
-        <v>6664736</v>
+        <v>6664831</v>
       </c>
       <c r="S7" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1315,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre tall med många ringhack några meter upp på stammen</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131429277</v>
+        <v>131429717</v>
       </c>
       <c r="B8" t="n">
-        <v>57909</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,16 +1358,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1378,7 +1378,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>489954</v>
+        <v>489814</v>
       </c>
       <c r="R8" t="n">
-        <v>6664687</v>
+        <v>6664870</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:09</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD8" t="b">
